--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F85CD3-F9E6-204D-B44C-B48A8C11126E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164D6079-228E-DA4B-8E0E-B02D0224F882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="136">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -331,42 +331,12 @@
     <t>output data</t>
   </si>
   <si>
-    <t>titlu</t>
-  </si>
-  <si>
-    <t>regizor</t>
-  </si>
-  <si>
-    <t>an aparitie</t>
-  </si>
-  <si>
-    <t>actori</t>
-  </si>
-  <si>
     <t>categorie</t>
   </si>
   <si>
-    <t>cuvinte cheie</t>
-  </si>
-  <si>
     <t>expected</t>
   </si>
   <si>
-    <t>"Movie Title"</t>
-  </si>
-  <si>
-    <t>Actor1, Actor2</t>
-  </si>
-  <si>
-    <t>keyword1, keyword2</t>
-  </si>
-  <si>
-    <t>2,3,2</t>
-  </si>
-  <si>
-    <t>record added</t>
-  </si>
-  <si>
     <t>…</t>
   </si>
   <si>
@@ -379,15 +349,6 @@
     <t>""</t>
   </si>
   <si>
-    <t>..</t>
-  </si>
-  <si>
-    <t>201q</t>
-  </si>
-  <si>
-    <t>Error message-? Compiler checked</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -421,18 +382,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>"M"</t>
-  </si>
-  <si>
-    <t>Drama</t>
-  </si>
-  <si>
-    <t>"M…123"</t>
-  </si>
-  <si>
-    <t>"M…12"</t>
-  </si>
-  <si>
     <t>BBT TCs</t>
   </si>
   <si>
@@ -457,25 +406,13 @@
     <t>TC1_ECP</t>
   </si>
   <si>
-    <t>Director1, Director2</t>
-  </si>
-  <si>
     <t>TC3_ECP</t>
   </si>
   <si>
-    <t>Error message-Empty movie title</t>
-  </si>
-  <si>
-    <t>TC5_ECP</t>
-  </si>
-  <si>
     <t>TC3_BVA</t>
   </si>
   <si>
     <t>TC4_BVA</t>
-  </si>
-  <si>
-    <t>TC5_BVA</t>
   </si>
   <si>
     <t>Statistics</t>
@@ -602,105 +539,6 @@
     <t>F01. adăugarea unui produs nou(id, nume, pret, tip, categorie, descriere)</t>
   </si>
   <si>
-    <t>ID_TC</t>
-  </si>
-  <si>
-    <t>Denumire / Scurtă descriere</t>
-  </si>
-  <si>
-    <t>Date de intrare (Input data)</t>
-  </si>
-  <si>
-    <t>Rezultat așteptat (Expected output)</t>
-  </si>
-  <si>
-    <t>Rezultat (Passed/Failed)</t>
-  </si>
-  <si>
-    <t>ID Bug</t>
-  </si>
-  <si>
-    <t>TC01</t>
-  </si>
-  <si>
-    <t>ECP Valid: Nume valid ($2 \leq \text{lungime} \leq 100$)</t>
-  </si>
-  <si>
-    <t>name="Latte", price=15.50</t>
-  </si>
-  <si>
-    <t>Produs adăugat cu succes</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>TC02</t>
-  </si>
-  <si>
-    <t>ECP Invalid: Nume prea scurt</t>
-  </si>
-  <si>
-    <t>name="A", price=15.50</t>
-  </si>
-  <si>
-    <t>ValidationException</t>
-  </si>
-  <si>
-    <t>TC03</t>
-  </si>
-  <si>
-    <t>ECP Valid: Preț valid ($0.01 \leq \text{preț} \leq 10000$)</t>
-  </si>
-  <si>
-    <t>name="Espresso", price=99.99</t>
-  </si>
-  <si>
-    <t>TC04</t>
-  </si>
-  <si>
-    <t>ECP Invalid: Preț negativ</t>
-  </si>
-  <si>
-    <t>name="Americano", price=-1.00</t>
-  </si>
-  <si>
-    <t>TC05</t>
-  </si>
-  <si>
-    <t>BVA Valid: Nume lungime minimă (1)*</t>
-  </si>
-  <si>
-    <t>name="N", price=10.00</t>
-  </si>
-  <si>
-    <t>TC06</t>
-  </si>
-  <si>
-    <t>BVA Valid: Nume peste limita minimă (2)</t>
-  </si>
-  <si>
-    <t>name="NN", price=10.00</t>
-  </si>
-  <si>
-    <t>TC07</t>
-  </si>
-  <si>
-    <t>BVA Invalid: Nume nul (limita de jos)</t>
-  </si>
-  <si>
-    <t>name=null, price=10.00</t>
-  </si>
-  <si>
-    <t>TC08</t>
-  </si>
-  <si>
-    <t>BVA Invalid: Nume blank</t>
-  </si>
-  <si>
-    <t>name=" ", price=10.00</t>
-  </si>
-  <si>
     <t>nume is not blank</t>
   </si>
   <si>
@@ -788,6 +626,9 @@
     <t>3,4</t>
   </si>
   <si>
+    <t>TC1_BVA</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
@@ -797,6 +638,9 @@
     <t>CLASIC_COFFEE</t>
   </si>
   <si>
+    <t>TC2_BVA</t>
+  </si>
+  <si>
     <t>TC1_EC</t>
   </si>
   <si>
@@ -828,13 +672,25 @@
   </si>
   <si>
     <t>error- price must be &gt;0</t>
+  </si>
+  <si>
+    <t>TC2_ECP</t>
+  </si>
+  <si>
+    <t>TC4_ECP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">error thrown </t>
+  </si>
+  <si>
+    <t>error - price must be &gt; 0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -946,14 +802,6 @@
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1093,7 +941,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1289,30 +1137,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1519,7 +1343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1537,25 +1361,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1595,17 +1415,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1618,23 +1438,23 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1688,48 +1508,48 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1757,7 +1577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1766,122 +1586,89 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2200,24 +1987,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="H1" s="51" t="s">
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="53"/>
+      <c r="H1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H2" s="56" t="s">
+      <c r="H2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H3" s="2"/>
@@ -2243,7 +2030,7 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="37"/>
+      <c r="B6" s="35"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
@@ -2252,7 +2039,7 @@
     </row>
     <row r="7" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="47" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2313,7 +2100,7 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="47" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2323,7 +2110,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="45" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2367,25 +2154,25 @@
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="48"/>
-      <c r="B24" s="52" t="s">
+      <c r="A24" s="46"/>
+      <c r="B24" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="52"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C26" s="50"/>
+      <c r="C26" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2422,260 +2209,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B3" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
+      <c r="B3" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="75"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="G5" s="79" t="s">
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="G5" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="80" t="s">
+      <c r="G6" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="66" t="s">
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="66"/>
+      <c r="O6" s="64"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="72" t="s">
-        <v>94</v>
+      <c r="C7" s="70" t="s">
+        <v>73</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="N7" s="62" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="63"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="61"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="72"/>
+      <c r="C8" s="70"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" s="23">
+        <v>75</v>
+      </c>
+      <c r="G8" s="21">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="J8" s="2">
         <v>15.5</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="N8" s="58" t="s">
-        <v>153</v>
-      </c>
-      <c r="O8" s="59"/>
+        <v>98</v>
+      </c>
+      <c r="N8" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" s="57"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="72" t="s">
-        <v>97</v>
+      <c r="C9" s="70" t="s">
+        <v>76</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="23">
+      <c r="G9" s="21">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J9" s="2">
         <v>16.5</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="N9" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="O9" s="59"/>
+        <v>98</v>
+      </c>
+      <c r="N9" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="O9" s="57"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="72"/>
+      <c r="C10" s="70"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="34">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" s="13">
+        <v>99.99</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="36">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J10" s="14">
-        <v>99.99</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="N10" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="O10" s="71"/>
+      <c r="N10" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="69"/>
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="72" t="s">
-        <v>99</v>
+      <c r="C11" s="70" t="s">
+        <v>78</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="36">
+      <c r="G11" s="34">
         <v>4</v>
       </c>
-      <c r="H11" s="14" t="s">
-        <v>155</v>
+      <c r="H11" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J11" s="14">
+        <v>95</v>
+      </c>
+      <c r="J11" s="13">
         <v>-1</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="N11" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="O11" s="59"/>
+        <v>98</v>
+      </c>
+      <c r="N11" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="57"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="72"/>
+      <c r="C12" s="70"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="13">
+        <v>79</v>
+      </c>
+      <c r="G12" s="12">
         <v>5</v>
       </c>
       <c r="H12" s="9"/>
@@ -2684,21 +2471,21 @@
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="69"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="73" t="s">
-        <v>101</v>
+      <c r="C13" s="71" t="s">
+        <v>80</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>6</v>
       </c>
       <c r="H13" s="9"/>
@@ -2707,329 +2494,221 @@
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="69"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="67"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="74"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" s="19">
+        <v>81</v>
+      </c>
+      <c r="G14" s="17">
         <v>7</v>
       </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="60"/>
-      <c r="O14" s="61"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="59"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="72" t="s">
-        <v>103</v>
+      <c r="C15" s="70" t="s">
+        <v>82</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E15" s="4"/>
-      <c r="G15" s="19">
+      <c r="G15" s="17">
         <v>8</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="61"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="59"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="72"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="61"/>
+        <v>83</v>
+      </c>
+      <c r="G16" s="17"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="59"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="72" t="s">
-        <v>105</v>
+      <c r="C17" s="70" t="s">
+        <v>84</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E17" s="4"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="61"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="59"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="72"/>
+      <c r="C18" s="70"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="61"/>
+        <v>85</v>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="59"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="72" t="s">
-        <v>141</v>
+      <c r="C19" s="70" t="s">
+        <v>87</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="E19" s="4"/>
-      <c r="G19" s="23"/>
+      <c r="G19" s="21"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="61"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="59"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="72"/>
+      <c r="C20" s="70"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="D22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
+        <v>38</v>
+      </c>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G25" s="134" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25" s="134" t="s">
-        <v>109</v>
-      </c>
-      <c r="I25" s="134" t="s">
-        <v>110</v>
-      </c>
-      <c r="J25" s="134" t="s">
-        <v>111</v>
-      </c>
-      <c r="K25" s="134" t="s">
-        <v>112</v>
-      </c>
-      <c r="L25" s="134" t="s">
-        <v>113</v>
-      </c>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G26" s="134" t="s">
-        <v>114</v>
-      </c>
-      <c r="H26" s="135" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26" s="135" t="s">
-        <v>116</v>
-      </c>
-      <c r="J26" s="135" t="s">
-        <v>117</v>
-      </c>
-      <c r="K26" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L26" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G26" s="119"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G27" s="134" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" s="135" t="s">
-        <v>120</v>
-      </c>
-      <c r="I27" s="135" t="s">
-        <v>121</v>
-      </c>
-      <c r="J27" s="135" t="s">
-        <v>122</v>
-      </c>
-      <c r="K27" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L27" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G27" s="119"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G28" s="134" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28" s="135" t="s">
-        <v>124</v>
-      </c>
-      <c r="I28" s="135" t="s">
-        <v>125</v>
-      </c>
-      <c r="J28" s="135" t="s">
-        <v>117</v>
-      </c>
-      <c r="K28" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L28" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G28" s="119"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G29" s="134" t="s">
-        <v>126</v>
-      </c>
-      <c r="H29" s="135" t="s">
-        <v>127</v>
-      </c>
-      <c r="I29" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="J29" s="135" t="s">
-        <v>122</v>
-      </c>
-      <c r="K29" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L29" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G29" s="119"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="120"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="120"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G30" s="134" t="s">
-        <v>129</v>
-      </c>
-      <c r="H30" s="135" t="s">
-        <v>130</v>
-      </c>
-      <c r="I30" s="135" t="s">
-        <v>131</v>
-      </c>
-      <c r="J30" s="135" t="s">
-        <v>117</v>
-      </c>
-      <c r="K30" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L30" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G30" s="119"/>
+      <c r="H30" s="120"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="120"/>
+      <c r="L30" s="120"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G31" s="134" t="s">
-        <v>132</v>
-      </c>
-      <c r="H31" s="135" t="s">
-        <v>133</v>
-      </c>
-      <c r="I31" s="135" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" s="135" t="s">
-        <v>117</v>
-      </c>
-      <c r="K31" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L31" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G31" s="119"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G32" s="134" t="s">
-        <v>135</v>
-      </c>
-      <c r="H32" s="135" t="s">
-        <v>136</v>
-      </c>
-      <c r="I32" s="135" t="s">
-        <v>137</v>
-      </c>
-      <c r="J32" s="135" t="s">
-        <v>122</v>
-      </c>
-      <c r="K32" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L32" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G32" s="119"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="120"/>
+      <c r="K32" s="120"/>
+      <c r="L32" s="120"/>
     </row>
     <row r="33" spans="7:12" x14ac:dyDescent="0.2">
-      <c r="G33" s="134" t="s">
-        <v>138</v>
-      </c>
-      <c r="H33" s="135" t="s">
-        <v>139</v>
-      </c>
-      <c r="I33" s="135" t="s">
-        <v>140</v>
-      </c>
-      <c r="J33" s="135" t="s">
-        <v>122</v>
-      </c>
-      <c r="K33" s="135" t="s">
-        <v>118</v>
-      </c>
-      <c r="L33" s="135" t="s">
-        <v>46</v>
-      </c>
+      <c r="G33" s="119"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="120"/>
+      <c r="K33" s="120"/>
+      <c r="L33" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -3094,588 +2773,588 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B3" s="133" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
+      <c r="B3" s="118" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="75"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B5" s="88" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
+      <c r="B5" s="86" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
+      <c r="G5" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
     </row>
     <row r="6" spans="2:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="80" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="80" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="84" t="s">
+      <c r="G6" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="84" t="s">
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
+      <c r="P6" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="86"/>
+      <c r="Q6" s="84"/>
     </row>
     <row r="7" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="73">
+      <c r="B7" s="71">
         <v>1</v>
       </c>
-      <c r="C7" s="90" t="s">
-        <v>156</v>
+      <c r="C7" s="88" t="s">
+        <v>102</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="M7" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="N7" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="P7" s="62" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="63"/>
+        <v>103</v>
+      </c>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="M7" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="N7" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="P7" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="61"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B8" s="89"/>
-      <c r="C8" s="91"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" s="23">
+        <v>104</v>
+      </c>
+      <c r="G8" s="21">
         <v>1</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="L8" s="34">
+      <c r="H8" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="L8" s="32">
         <v>10</v>
       </c>
-      <c r="M8" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="O8" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="P8" s="82" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q8" s="83"/>
+      <c r="M8" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="O8" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="P8" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q8" s="81"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B9" s="89"/>
-      <c r="C9" s="91"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="89"/>
       <c r="D9" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" s="19">
+        <v>105</v>
+      </c>
+      <c r="G9" s="17">
         <v>2</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="18">
         <v>5</v>
       </c>
-      <c r="I9" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="L9" s="34">
+      <c r="I9" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L9" s="32">
         <v>10</v>
       </c>
-      <c r="M9" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="O9" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="P9" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q9" s="69"/>
+      <c r="M9" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="P9" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q9" s="67"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B10" s="89"/>
-      <c r="C10" s="91"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G10" s="23">
+        <v>106</v>
+      </c>
+      <c r="G10" s="21">
         <v>3</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="K10" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="O10" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="P10" s="82" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q10" s="83"/>
+      <c r="H10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="M10" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="P10" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="81"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="89"/>
-      <c r="C11" s="91"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G11" s="23">
+        <v>107</v>
+      </c>
+      <c r="G11" s="21">
         <v>4</v>
       </c>
-      <c r="H11" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="K11" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="L11" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="M11" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="N11" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="O11" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="P11" s="82" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q11" s="83"/>
+      <c r="H11" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="O11" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="P11" s="80" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q11" s="81"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B12" s="74"/>
-      <c r="C12" s="92"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="90"/>
       <c r="D12" s="2"/>
-      <c r="G12" s="23">
+      <c r="G12" s="21">
         <v>5</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="83"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="81"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="73">
+      <c r="B13" s="71">
         <v>2</v>
       </c>
-      <c r="C13" s="73" t="s">
-        <v>162</v>
+      <c r="C13" s="71" t="s">
+        <v>108</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G13" s="19">
+        <v>109</v>
+      </c>
+      <c r="G13" s="17">
         <v>6</v>
       </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="69"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="67"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
       <c r="D14" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G14" s="23">
+        <v>110</v>
+      </c>
+      <c r="G14" s="21">
         <v>7</v>
       </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="83"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="81"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G15" s="23">
+        <v>111</v>
+      </c>
+      <c r="G15" s="21">
         <v>8</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="83"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="81"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="23">
+        <v>112</v>
+      </c>
+      <c r="G16" s="21">
         <v>9</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="83"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="81"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G17" s="23">
+        <v>113</v>
+      </c>
+      <c r="G17" s="21">
         <v>10</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="82"/>
-      <c r="Q17" s="83"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="81"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
       <c r="D18" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G18" s="23">
+        <v>114</v>
+      </c>
+      <c r="G18" s="21">
         <v>11</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="82"/>
-      <c r="Q18" s="83"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="81"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B19" s="73">
+      <c r="B19" s="71">
         <v>3</v>
       </c>
-      <c r="C19" s="90"/>
+      <c r="C19" s="88"/>
       <c r="D19" s="2"/>
-      <c r="G19" s="23">
+      <c r="G19" s="21">
         <v>12</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="83"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="81"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B20" s="89"/>
-      <c r="C20" s="91"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="89"/>
       <c r="D20" s="2"/>
-      <c r="G20" s="23">
+      <c r="G20" s="21">
         <v>13</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="83"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="81"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B21" s="89"/>
-      <c r="C21" s="91"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="89"/>
       <c r="D21" s="2"/>
-      <c r="G21" s="23">
+      <c r="G21" s="21">
         <v>14</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="82"/>
-      <c r="Q21" s="83"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="81"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B22" s="89"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="89"/>
       <c r="D22" s="2"/>
-      <c r="G22" s="23">
+      <c r="G22" s="21">
         <v>15</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="82"/>
-      <c r="Q22" s="83"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="81"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B23" s="89"/>
-      <c r="C23" s="91"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="2"/>
-      <c r="G23" s="23">
+      <c r="G23" s="21">
         <v>16</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="82"/>
-      <c r="Q23" s="83"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="81"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B24" s="74"/>
-      <c r="C24" s="92"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="2"/>
-      <c r="G24" s="23">
+      <c r="G24" s="21">
         <v>17</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="83"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="81"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B25" s="73">
+      <c r="B25" s="71">
         <v>4</v>
       </c>
-      <c r="C25" s="90" t="s">
-        <v>44</v>
+      <c r="C25" s="88" t="s">
+        <v>34</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="23">
+        <v>34</v>
+      </c>
+      <c r="G25" s="21">
         <v>18</v>
       </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="82"/>
-      <c r="Q25" s="83"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="81"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B26" s="89"/>
-      <c r="C26" s="91"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B27" s="89"/>
-      <c r="C27" s="91"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B28" s="89"/>
-      <c r="C28" s="91"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="43"/>
+        <v>34</v>
+      </c>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="41"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B29" s="89"/>
-      <c r="C29" s="91"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="89"/>
       <c r="D29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="44"/>
+        <v>34</v>
+      </c>
+      <c r="I29" s="91"/>
+      <c r="J29" s="91"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="91"/>
+      <c r="M29" s="91"/>
+      <c r="N29" s="42"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B30" s="74"/>
-      <c r="C30" s="92"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="90"/>
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -3732,7 +3411,7 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B1:P21"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -3740,582 +3419,510 @@
     <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" customWidth="1"/>
-    <col min="13" max="13" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B1" s="53" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="132" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="132"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="80" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="126" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="106" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="62" t="s">
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B3" s="117" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="117"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="115" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="66" t="s">
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="66"/>
-    </row>
-    <row r="5" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="26" t="s">
+      <c r="L4" s="64"/>
+    </row>
+    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="102"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="J5" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="L5" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="22">
+        <v>1</v>
+      </c>
+      <c r="C6" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="119" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="120"/>
-      <c r="M5" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="24">
-        <v>1</v>
-      </c>
-      <c r="C6" s="103" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="29">
-        <v>2010</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="121" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="122" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="12">
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="11">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="8">
-        <v>2010</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="128" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="129"/>
-      <c r="M7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="12">
+      <c r="C7" s="100"/>
+      <c r="D7" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="11">
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="103"/>
-      <c r="D8" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>63</v>
+      <c r="C8" s="100"/>
+      <c r="D8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="13">
+        <v>99.99</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="12">
+        <v>99</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="131"/>
-      <c r="M9" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="12">
+      <c r="C9" s="100"/>
+      <c r="D9" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="13">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="123" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" s="124"/>
-      <c r="M10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="12">
+      <c r="C10" s="100"/>
+      <c r="D10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="32">
+        <v>10</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" s="123" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" s="124"/>
-      <c r="M11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B12" s="12">
+      <c r="C11" s="100"/>
+      <c r="D11" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="32">
+        <v>10</v>
+      </c>
+      <c r="H11" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12" s="123" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="124"/>
-      <c r="M12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="25">
+      <c r="C12" s="100"/>
+      <c r="D12" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="23">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="104"/>
-      <c r="D13" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="117" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="118"/>
-      <c r="M13" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="N13" s="25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-    </row>
-    <row r="15" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" s="122" t="s">
+        <v>135</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="2:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="96" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17" s="96" t="s">
-        <v>84</v>
-      </c>
-      <c r="I17" s="97"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="96" t="s">
-        <v>85</v>
-      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="94" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="96"/>
+      <c r="E17" s="96"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="95"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="L17" s="95"/>
+      <c r="M17" s="96"/>
       <c r="N17" s="97"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="99"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="110" t="s">
+    </row>
+    <row r="18" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="107" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="108" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="93" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="95" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="94" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="116" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="112" t="s">
-        <v>91</v>
-      </c>
-      <c r="I18" s="113"/>
-      <c r="J18" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="K18" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="M18" s="100" t="s">
-        <v>91</v>
-      </c>
-      <c r="N18" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="O18" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="P18" s="94" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="114"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="101"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="95"/>
-      <c r="P19" s="94"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B20" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="38">
+      <c r="G18" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="109" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="110"/>
+      <c r="J18" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="K18" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="N18" s="92" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="93"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="93"/>
+      <c r="M19" s="93"/>
+      <c r="N19" s="92"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="36">
         <v>8</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="38">
         <v>5</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="38">
         <v>3</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="108" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="109"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="105" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="106"/>
       <c r="J20" s="2">
         <v>3</v>
       </c>
-      <c r="K20" s="40">
-        <v>3</v>
-      </c>
-      <c r="L20" s="41">
+      <c r="K20" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="L20" s="2">
+        <v>5</v>
+      </c>
+      <c r="M20" s="38">
+        <v>5</v>
+      </c>
+      <c r="N20" s="39">
         <v>0</v>
       </c>
-      <c r="M20" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="N20" s="2">
-        <v>5</v>
-      </c>
-      <c r="O20" s="40">
-        <v>5</v>
-      </c>
-      <c r="P20" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="M21" s="3"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="K21" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="25">
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F4:J4"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="B3:L3"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -4327,16 +3934,14 @@
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="H18:I19"/>
     <mergeCell ref="G18:G19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="K17:N17"/>
     <mergeCell ref="K18:K19"/>
     <mergeCell ref="L18:L19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
